--- a/docs/Manussa-your-pieces.xlsx
+++ b/docs/Manussa-your-pieces.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -508,8 +508,9 @@
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="54" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -591,8 +592,13 @@
           <t>How should it be cleaned?</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Describe it — what makes it special?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Painted Capelet</t>
@@ -607,8 +613,9 @@
       <c r="H6" s="9" t="n"/>
       <c r="I6" s="10" t="n"/>
       <c r="J6" s="10" t="n"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+      <c r="K6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="54" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Column Gown</t>
@@ -623,8 +630,9 @@
       <c r="H7" s="9" t="n"/>
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="10" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+      <c r="K7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Painted Corset Bodice</t>
@@ -639,8 +647,9 @@
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="10" t="n"/>
       <c r="J8" s="10" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+      <c r="K8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="54" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Raw Silk Fluted Skirt</t>
@@ -655,8 +664,9 @@
       <c r="H9" s="9" t="n"/>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="10" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+      <c r="K9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Elegant Powerful Jacket</t>
@@ -671,8 +681,9 @@
       <c r="H10" s="9" t="n"/>
       <c r="I10" s="10" t="n"/>
       <c r="J10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+      <c r="K10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="54" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Crimson Drive Jacket</t>
@@ -687,8 +698,9 @@
       <c r="H11" s="9" t="n"/>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="10" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+      <c r="K11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="54" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Men's Panelled Jacket</t>
@@ -703,8 +715,9 @@
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="10" t="n"/>
       <c r="J12" s="10" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
+      <c r="K12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Melting Paint Denim Jacket</t>
@@ -719,8 +732,9 @@
       <c r="H13" s="9" t="n"/>
       <c r="I13" s="10" t="n"/>
       <c r="J13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+      <c r="K13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="54" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Indigo Panel Denim Jacket</t>
@@ -735,8 +749,9 @@
       <c r="H14" s="9" t="n"/>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="10" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+      <c r="K14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="54" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>New Traditional Patchwork Jacket</t>
@@ -751,8 +766,9 @@
       <c r="H15" s="9" t="n"/>
       <c r="I15" s="10" t="n"/>
       <c r="J15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+      <c r="K15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="54" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Mosaic Peplum Top</t>
@@ -767,8 +783,9 @@
       <c r="H16" s="9" t="n"/>
       <c r="I16" s="10" t="n"/>
       <c r="J16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+      <c r="K16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="54" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Coral Embroidered Gown</t>
@@ -783,8 +800,9 @@
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="10" t="n"/>
       <c r="J17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+      <c r="K17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="54" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Structured Peplum Vest</t>
@@ -799,6 +817,7 @@
       <c r="H18" s="9" t="n"/>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="10" t="n"/>
+      <c r="K18" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/Manussa-your-pieces.xlsx
+++ b/docs/Manussa-your-pieces.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Your pieces" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Your designers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,9 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -104,32 +103,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -497,20 +484,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="54" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,304 +510,286 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Prices are in US dollars — tell me if you would rather sell in kyat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>how many you have of each size</t>
+          <t>The website does not sell anything, so nothing here asks for a price.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Piece</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>XS</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>XXL</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>What is it made of?</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>How should it be cleaned?</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Describe it — what makes it special?</t>
         </is>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Painted Capelet</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9" t="n"/>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="10" t="n"/>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="10" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Column Gown</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="10" t="n"/>
-      <c r="J7" s="10" t="n"/>
-      <c r="K7" s="10" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Painted Corset Bodice</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="10" t="n"/>
-      <c r="J8" s="10" t="n"/>
-      <c r="K8" s="10" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Raw Silk Fluted Skirt</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="10" t="n"/>
-      <c r="J9" s="10" t="n"/>
-      <c r="K9" s="10" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Elegant Powerful Jacket</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="10" t="n"/>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="10" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Crimson Drive Jacket</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="10" t="n"/>
-      <c r="J11" s="10" t="n"/>
-      <c r="K11" s="10" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Men's Panelled Jacket</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Melting Paint Denim Jacket</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="10" t="n"/>
-      <c r="J13" s="10" t="n"/>
-      <c r="K13" s="10" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Indigo Panel Denim Jacket</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="10" t="n"/>
-      <c r="J14" s="10" t="n"/>
-      <c r="K14" s="10" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>New Traditional Patchwork Jacket</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="10" t="n"/>
-      <c r="J15" s="10" t="n"/>
-      <c r="K15" s="10" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
     </row>
     <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Mosaic Peplum Top</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="10" t="n"/>
-      <c r="J16" s="10" t="n"/>
-      <c r="K16" s="10" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
     </row>
     <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Coral Embroidered Gown</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="10" t="n"/>
-      <c r="J17" s="10" t="n"/>
-      <c r="K17" s="10" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Structured Peplum Vest</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="9" t="n"/>
-      <c r="H18" s="9" t="n"/>
-      <c r="I18" s="10" t="n"/>
-      <c r="J18" s="10" t="n"/>
-      <c r="K18" s="10" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Your designers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Each designer has their own page on the website, showing the pieces they made. Right now the pages have no words about the person — only their work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>A sentence or two each is plenty. Leave blank anyone who would rather not have one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>What they do</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>A sentence or two about them</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Katherine Paing</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Ei Ko Zin Latt</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Pan Ywal Oo</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Sa Thaw Zin Hut</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Kay</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Sandi</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Win Min Than</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="C6:H18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Whole numbers only" error="Please type a whole number — 0, 1, 2 and so on." type="whole" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>